--- a/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-corepatient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
